--- a/markup.xlsx
+++ b/markup.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nadyshka\Desktop\LEARNING\Задачи собесные\Тестовое ЗЯ\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBD5A42-44EA-4EAC-AB56-BCF0B1B4D1BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,350 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="112">
+  <si>
+    <t>Сегмент рынка</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Бренд</t>
+  </si>
+  <si>
+    <t>Продукт</t>
+  </si>
+  <si>
+    <t>Дата начала</t>
+  </si>
+  <si>
+    <t>Дата окончания</t>
+  </si>
+  <si>
+    <t>Наценка</t>
+  </si>
+  <si>
+    <t>Активный</t>
+  </si>
+  <si>
+    <t>Люкс</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>Массмаркет</t>
+  </si>
+  <si>
+    <t>Макияж</t>
+  </si>
+  <si>
+    <t>Уход</t>
+  </si>
+  <si>
+    <t>Брови</t>
+  </si>
+  <si>
+    <t>Авто загар</t>
+  </si>
+  <si>
+    <t>Clarins</t>
+  </si>
+  <si>
+    <t>Аксессуары_уход</t>
+  </si>
+  <si>
+    <t>Антицеллюлитная серия/коррекция фигуры</t>
+  </si>
+  <si>
+    <t>База под тушь</t>
+  </si>
+  <si>
+    <t>Бальзам для лица</t>
+  </si>
+  <si>
+    <t>Бальзамы для губ</t>
+  </si>
+  <si>
+    <t>Блеск для губ</t>
+  </si>
+  <si>
+    <t>Бронзер</t>
+  </si>
+  <si>
+    <t>ВВ/СС средства</t>
+  </si>
+  <si>
+    <t>Гель для бритья</t>
+  </si>
+  <si>
+    <t>Нет</t>
+  </si>
+  <si>
+    <t>Гель для бровей</t>
+  </si>
+  <si>
+    <t>Гель для душа</t>
+  </si>
+  <si>
+    <t>Гель для лица</t>
+  </si>
+  <si>
+    <t>Гель для умывания</t>
+  </si>
+  <si>
+    <t>Гель после бритья</t>
+  </si>
+  <si>
+    <t>Гидрофильные средства</t>
+  </si>
+  <si>
+    <t>Жидкая подводка</t>
+  </si>
+  <si>
+    <t>Жидкие тональные основы</t>
+  </si>
+  <si>
+    <t>Защита от 21 до 30 SPF</t>
+  </si>
+  <si>
+    <t>Защита от 41 до 50 SPF</t>
+  </si>
+  <si>
+    <t>Карандаш для бровей</t>
+  </si>
+  <si>
+    <t>Карандаш для глаз</t>
+  </si>
+  <si>
+    <t>Карандаш для губ</t>
+  </si>
+  <si>
+    <t>Кисти</t>
+  </si>
+  <si>
+    <t>Классическая помада</t>
+  </si>
+  <si>
+    <t>Компактная пудра</t>
+  </si>
+  <si>
+    <t>Корректор/консилер</t>
+  </si>
+  <si>
+    <t>Косметическая вода</t>
+  </si>
+  <si>
+    <t>Крем для лица</t>
+  </si>
+  <si>
+    <t>Крем для ног</t>
+  </si>
+  <si>
+    <t>Крем для рук</t>
+  </si>
+  <si>
+    <t>Крем для тела</t>
+  </si>
+  <si>
+    <t>Лосьон после бритья</t>
+  </si>
+  <si>
+    <t>Маркеры</t>
+  </si>
+  <si>
+    <t>Масла</t>
+  </si>
+  <si>
+    <t>Масло для бритья</t>
+  </si>
+  <si>
+    <t>Масло для губ</t>
+  </si>
+  <si>
+    <t>Масло для лица</t>
+  </si>
+  <si>
+    <t>Мицеллярные средства</t>
+  </si>
+  <si>
+    <t>Молочко</t>
+  </si>
+  <si>
+    <t>Молочко для тела</t>
+  </si>
+  <si>
+    <t>Наборы_уход</t>
+  </si>
+  <si>
+    <t>Пена для ванн</t>
+  </si>
+  <si>
+    <t>Пенка для умывания</t>
+  </si>
+  <si>
+    <t>Пилинг/скраб для лица</t>
+  </si>
+  <si>
+    <t>После загара</t>
+  </si>
+  <si>
+    <t>Праймер/база_лицо</t>
+  </si>
+  <si>
+    <t>Прессованные румяна</t>
+  </si>
+  <si>
+    <t>Прессованные тени</t>
+  </si>
+  <si>
+    <t>Прочее очищение/демакияж</t>
+  </si>
+  <si>
+    <t>Прочее_тело</t>
+  </si>
+  <si>
+    <t>Рассыпчатая пудра</t>
+  </si>
+  <si>
+    <t>Ролик</t>
+  </si>
+  <si>
+    <t>Скраб-пилинг для тела</t>
+  </si>
+  <si>
+    <t>Специальный уход</t>
+  </si>
+  <si>
+    <t>Спрей_дезодорант</t>
+  </si>
+  <si>
+    <t>Средства для век</t>
+  </si>
+  <si>
+    <t>Сыворотки</t>
+  </si>
+  <si>
+    <t>Тинт/пигмент</t>
+  </si>
+  <si>
+    <t>Тоники-лосьоны-тонеры</t>
+  </si>
+  <si>
+    <t>Тушь</t>
+  </si>
+  <si>
+    <t>Уход для губ_макияж</t>
+  </si>
+  <si>
+    <t>Уход за лицом _маски</t>
+  </si>
+  <si>
+    <t>Фиксаторы макияжа</t>
+  </si>
+  <si>
+    <t>Флюид</t>
+  </si>
+  <si>
+    <t>Футляры/кейсы/палитры</t>
+  </si>
+  <si>
+    <t>Эмульсии</t>
+  </si>
+  <si>
+    <t>Эссенция</t>
+  </si>
+  <si>
+    <t>Vivienne Sabo</t>
+  </si>
+  <si>
+    <t>Гелевые подводки</t>
+  </si>
+  <si>
+    <t>Жидкая помада для губ</t>
+  </si>
+  <si>
+    <t>Кремовые румяна</t>
+  </si>
+  <si>
+    <t>Маркеры для бровей</t>
+  </si>
+  <si>
+    <t>Наборы_макияж</t>
+  </si>
+  <si>
+    <t>Палетки_брови</t>
+  </si>
+  <si>
+    <t>Палетки_глаза</t>
+  </si>
+  <si>
+    <t>Палетки_лицо</t>
+  </si>
+  <si>
+    <t>Патчи_глаза</t>
+  </si>
+  <si>
+    <t>Помада для губ_прочее</t>
+  </si>
+  <si>
+    <t>Тушь для бровей</t>
+  </si>
+  <si>
+    <t>Тушь для ресниц</t>
+  </si>
+  <si>
+    <t>Уход для бровей</t>
+  </si>
+  <si>
+    <t>Хайлайтер/люминайзер</t>
+  </si>
+  <si>
+    <t>Аксессуары_прочее</t>
+  </si>
+  <si>
+    <t>База/праймер_глаза</t>
+  </si>
+  <si>
+    <t>Глиттер/шиммер (блестки)</t>
+  </si>
+  <si>
+    <t>Контуринг</t>
+  </si>
+  <si>
+    <t>Кремовые/жидкие тени</t>
+  </si>
+  <si>
+    <t>Матирующие салфетки</t>
+  </si>
+  <si>
+    <t>Пилки для ногтей</t>
+  </si>
+  <si>
+    <t>Помада-карандаш/стик</t>
+  </si>
+  <si>
+    <t>Точилки</t>
+  </si>
+  <si>
+    <t>19000217070</t>
+  </si>
+  <si>
+    <t>19000419067</t>
+  </si>
+  <si>
+    <t>19000359936</t>
+  </si>
+  <si>
+    <t>14035900003</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +375,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,15 +413,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{D94E9C0B-51BF-4200-806E-84028DAA3334}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +730,2237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H124"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="H12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="H14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="5">
+        <v>0.87</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="H19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="5">
+        <v>0.93</v>
+      </c>
+      <c r="H20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="H22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="H24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="H27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="H28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="H29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="H32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="H33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="5">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="H37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="H38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="H40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="H41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="H42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="H43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="H47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="H49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="H50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="H51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="H55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="H56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="H58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="H60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5">
+        <v>0.93</v>
+      </c>
+      <c r="H61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="H62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="5">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="5">
+        <v>1.06</v>
+      </c>
+      <c r="H65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="5">
+        <v>1.08</v>
+      </c>
+      <c r="H66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="5">
+        <v>0.88</v>
+      </c>
+      <c r="H67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F68" s="4"/>
+      <c r="G68" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="H68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="G69" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H69" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="H70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F72" s="4">
+        <v>45778</v>
+      </c>
+      <c r="G72" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H73" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F74" s="4"/>
+      <c r="G74" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="H74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F75" s="4"/>
+      <c r="G75" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="H75" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F76" s="4"/>
+      <c r="G76" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H76" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F77" s="4"/>
+      <c r="G77" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="H77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C78" t="s">
+        <v>84</v>
+      </c>
+      <c r="E78" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F78" s="4"/>
+      <c r="G78" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="H78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="H79" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F80" s="4"/>
+      <c r="G80" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="H80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+      <c r="C81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F81" s="4"/>
+      <c r="G81" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="H81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F82" s="4"/>
+      <c r="G82" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="H82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F83" s="4"/>
+      <c r="G83" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="H83" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+      <c r="E84" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F84" s="4"/>
+      <c r="G84" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H84" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" t="s">
+        <v>84</v>
+      </c>
+      <c r="E85" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F85" s="4"/>
+      <c r="G85" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="H85" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="H86" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="H87" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F88" s="4"/>
+      <c r="G88" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H88" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" t="s">
+        <v>84</v>
+      </c>
+      <c r="E89" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F89" s="4"/>
+      <c r="G89" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="H89" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B90" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" t="s">
+        <v>84</v>
+      </c>
+      <c r="E90" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F90" s="4"/>
+      <c r="G90" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B91" t="s">
+        <v>87</v>
+      </c>
+      <c r="C91" t="s">
+        <v>84</v>
+      </c>
+      <c r="E91" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F91" s="4"/>
+      <c r="G91" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="H91" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92" t="s">
+        <v>84</v>
+      </c>
+      <c r="E92" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F92" s="4"/>
+      <c r="G92" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="H92" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>88</v>
+      </c>
+      <c r="C93" t="s">
+        <v>84</v>
+      </c>
+      <c r="E93" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F93" s="4"/>
+      <c r="G93" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="H93" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" t="s">
+        <v>84</v>
+      </c>
+      <c r="E94" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F94" s="4"/>
+      <c r="G94" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H94" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>90</v>
+      </c>
+      <c r="C95" t="s">
+        <v>84</v>
+      </c>
+      <c r="E95" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F95" s="4"/>
+      <c r="G95" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="H95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96" t="s">
+        <v>84</v>
+      </c>
+      <c r="E96" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F96" s="4"/>
+      <c r="G96" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" t="s">
+        <v>84</v>
+      </c>
+      <c r="E97" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F97" s="4"/>
+      <c r="G97" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>93</v>
+      </c>
+      <c r="C98" t="s">
+        <v>84</v>
+      </c>
+      <c r="E98" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F98" s="4"/>
+      <c r="G98" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="H98" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>94</v>
+      </c>
+      <c r="C99" t="s">
+        <v>84</v>
+      </c>
+      <c r="E99" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F99" s="4"/>
+      <c r="G99" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="H99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>76</v>
+      </c>
+      <c r="C100" t="s">
+        <v>84</v>
+      </c>
+      <c r="E100" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F100" s="4"/>
+      <c r="G100" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B101" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" t="s">
+        <v>84</v>
+      </c>
+      <c r="E101" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F101" s="4"/>
+      <c r="G101" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="H101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>96</v>
+      </c>
+      <c r="C102" t="s">
+        <v>84</v>
+      </c>
+      <c r="E102" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F102" s="4"/>
+      <c r="G102" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="H102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>97</v>
+      </c>
+      <c r="C103" t="s">
+        <v>84</v>
+      </c>
+      <c r="E103" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F103" s="4"/>
+      <c r="G103" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="H103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>77</v>
+      </c>
+      <c r="C104" t="s">
+        <v>84</v>
+      </c>
+      <c r="E104" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F104" s="4"/>
+      <c r="G104" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>98</v>
+      </c>
+      <c r="C105" t="s">
+        <v>84</v>
+      </c>
+      <c r="E105" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F105" s="4"/>
+      <c r="G105" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="H105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" t="s">
+        <v>84</v>
+      </c>
+      <c r="E106" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F106" s="4"/>
+      <c r="G106" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="H106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" t="s">
+        <v>84</v>
+      </c>
+      <c r="E107" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F107" s="4"/>
+      <c r="G107" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="H107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108" t="s">
+        <v>84</v>
+      </c>
+      <c r="E108" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F108" s="4"/>
+      <c r="G108" s="5">
+        <v>0.83</v>
+      </c>
+      <c r="H108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" t="s">
+        <v>84</v>
+      </c>
+      <c r="E109" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F109" s="4"/>
+      <c r="G109" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="H109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" t="s">
+        <v>84</v>
+      </c>
+      <c r="E110" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F110" s="4">
+        <v>45809</v>
+      </c>
+      <c r="G110" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="H110" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B111" t="s">
+        <v>37</v>
+      </c>
+      <c r="C111" t="s">
+        <v>84</v>
+      </c>
+      <c r="E111" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F111" s="4"/>
+      <c r="G111" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="H111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B112" t="s">
+        <v>102</v>
+      </c>
+      <c r="C112" t="s">
+        <v>84</v>
+      </c>
+      <c r="E112" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F112" s="4"/>
+      <c r="G112" s="5">
+        <v>0.54</v>
+      </c>
+      <c r="H112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B113" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" t="s">
+        <v>84</v>
+      </c>
+      <c r="E113" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F113" s="4"/>
+      <c r="G113" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="H113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B114" t="s">
+        <v>52</v>
+      </c>
+      <c r="C114" t="s">
+        <v>84</v>
+      </c>
+      <c r="E114" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="H114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>104</v>
+      </c>
+      <c r="C115" t="s">
+        <v>84</v>
+      </c>
+      <c r="E115" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="H115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>105</v>
+      </c>
+      <c r="C116" t="s">
+        <v>84</v>
+      </c>
+      <c r="E116" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="H116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C117" t="s">
+        <v>84</v>
+      </c>
+      <c r="E117" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F117" s="4"/>
+      <c r="G117" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="H117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B118" t="s">
+        <v>64</v>
+      </c>
+      <c r="C118" t="s">
+        <v>84</v>
+      </c>
+      <c r="E118" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F118" s="4"/>
+      <c r="G118" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="H118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
+        <v>107</v>
+      </c>
+      <c r="C119" t="s">
+        <v>84</v>
+      </c>
+      <c r="E119" s="4">
+        <v>45658</v>
+      </c>
+      <c r="F119" s="4"/>
+      <c r="G119" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="H119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B120" t="s">
+        <v>36</v>
+      </c>
+      <c r="C120" t="s">
+        <v>84</v>
+      </c>
+      <c r="E120" s="4">
+        <v>45809</v>
+      </c>
+      <c r="F120" s="4"/>
+      <c r="G120" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="H120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D121" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E121" s="4">
+        <v>45658</v>
+      </c>
+      <c r="G121" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="H121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D122" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E122" s="4">
+        <v>45658</v>
+      </c>
+      <c r="G122" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="H122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D123" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E123" s="4">
+        <v>45658</v>
+      </c>
+      <c r="G123" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="H123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D124" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E124" s="4">
+        <v>45658</v>
+      </c>
+      <c r="G124" s="5">
+        <v>2</v>
+      </c>
+      <c r="H124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/markup.xlsx
+++ b/markup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nadyshka\Desktop\LEARNING\Задачи собесные\Тестовое ЗЯ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBD5A42-44EA-4EAC-AB56-BCF0B1B4D1BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9508E-7B65-4C36-B2A2-A392D67FF221}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/markup.xlsx
+++ b/markup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nadyshka\Desktop\LEARNING\Задачи собесные\Тестовое ЗЯ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F9508E-7B65-4C36-B2A2-A392D67FF221}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3264DEDF-9493-4716-A3C6-01678E79BF0C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
